--- a/config/apartments.xlsx
+++ b/config/apartments.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="91">
   <si>
     <t xml:space="preserve">Квартира</t>
   </si>
@@ -124,6 +124,9 @@
     <t xml:space="preserve">Жанна</t>
   </si>
   <si>
+    <t xml:space="preserve">Двушка. Гигант</t>
+  </si>
+  <si>
     <t xml:space="preserve">Декабристов, 62</t>
   </si>
   <si>
@@ -142,9 +145,6 @@
     <t xml:space="preserve">Заслонова 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Общие</t>
-  </si>
-  <si>
     <t xml:space="preserve">улица Константина Заслонова, 9/4 3</t>
   </si>
   <si>
@@ -167,6 +167,132 @@
   </si>
   <si>
     <t xml:space="preserve">Заслонова 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14-я линия Васильевского острова, 31-33 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Елена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14-я. Елена 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рижский проспект, 72-74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Анастасия. Москва</t>
+  </si>
+  <si>
+    <t xml:space="preserve">улица Достоевского, 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Перепелицы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кондратьевский проспект, 64к9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Анастасия. Юг</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рыбка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Московский проспект, 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Анна Каштанова. Москва</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Московский_20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Верхне-Каменская улица, 11к1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Людмила Николаевна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Каменка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Московское шоссе, 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Валентина и Константин</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Победа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Планерная улица, 99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Планерная</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-й Предпортовый проезд, 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наталья Нестерова</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Предпортовая</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Некрасова, 37/20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Иланна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аристократ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пушкинская улица, 11 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Олег</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пушк 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пушкинская улица, 11 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Андрей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пушк 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пушкинская улица, 11 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Иван</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пушк 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">проспект Просвещения, 35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ирина Стукалова</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Просвет</t>
+  </si>
+  <si>
+    <t xml:space="preserve">улица Бабушкина, 84к2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Елена из ВторичкиГрупп</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бабушкина</t>
   </si>
 </sst>
 </file>
@@ -245,7 +371,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -272,6 +398,14 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -397,12 +531,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr defaultColWidth="11.5625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="6.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="6.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="44"/>
   </cols>
@@ -429,7 +563,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -443,6 +577,9 @@
       <c r="D2" s="1" t="n">
         <v>1500</v>
       </c>
+      <c r="E2" s="1" t="n">
+        <v>1000</v>
+      </c>
       <c r="F2" s="3"/>
       <c r="G2" s="4" t="s">
         <v>8</v>
@@ -458,6 +595,9 @@
       <c r="C3" s="1" t="n">
         <v>15000</v>
       </c>
+      <c r="D3" s="1" t="n">
+        <v>1300</v>
+      </c>
       <c r="E3" s="1" t="n">
         <v>500</v>
       </c>
@@ -473,6 +613,12 @@
         <v>12</v>
       </c>
       <c r="C4" s="1"/>
+      <c r="D4" s="1" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>1000</v>
+      </c>
       <c r="F4" s="2" t="s">
         <v>13</v>
       </c>
@@ -490,6 +636,9 @@
       <c r="C5" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="D5" s="1" t="n">
+        <v>1300</v>
+      </c>
       <c r="E5" s="1" t="n">
         <v>500</v>
       </c>
@@ -506,6 +655,12 @@
         <v>18</v>
       </c>
       <c r="C6" s="1"/>
+      <c r="D6" s="1" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>1000</v>
+      </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
       </c>
@@ -524,6 +679,9 @@
       <c r="C7" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="D7" s="1" t="n">
+        <v>1300</v>
+      </c>
       <c r="E7" s="1" t="n">
         <v>500</v>
       </c>
@@ -545,6 +703,9 @@
       <c r="C8" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="D8" s="1" t="n">
+        <v>1300</v>
+      </c>
       <c r="E8" s="1" t="n">
         <v>500</v>
       </c>
@@ -565,6 +726,9 @@
       <c r="C9" s="1" t="n">
         <v>30000</v>
       </c>
+      <c r="D9" s="1" t="n">
+        <v>1300</v>
+      </c>
       <c r="E9" s="1" t="n">
         <v>500</v>
       </c>
@@ -581,6 +745,12 @@
         <v>27</v>
       </c>
       <c r="C10" s="1"/>
+      <c r="D10" s="1" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>1000</v>
+      </c>
       <c r="F10" s="2" t="s">
         <v>28</v>
       </c>
@@ -617,60 +787,57 @@
         <v>70</v>
       </c>
       <c r="C12" s="1"/>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="1" t="n">
         <v>2500</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="1" t="n">
         <v>1500</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>1000</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="D14" s="0" t="n">
+      <c r="D14" s="1" t="n">
         <v>1300</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>1000</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" s="0" t="s">
         <v>40</v>
       </c>
     </row>
@@ -681,10 +848,10 @@
       <c r="B15" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15" s="1" t="n">
         <v>1300</v>
       </c>
       <c r="E15" s="1" t="n">
@@ -704,7 +871,7 @@
       <c r="B16" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16" s="1" t="n">
         <v>1300</v>
       </c>
       <c r="E16" s="1" t="n">
@@ -715,9 +882,6 @@
       </c>
       <c r="G16" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="H16" s="0" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -727,7 +891,7 @@
       <c r="B17" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="D17" s="1" t="n">
         <v>1300</v>
       </c>
       <c r="E17" s="1" t="n">
@@ -739,8 +903,306 @@
       <c r="G17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H17" s="0" t="s">
-        <v>40</v>
+    </row>
+    <row r="18" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/config/apartments.xlsx
+++ b/config/apartments.xlsx
@@ -371,7 +371,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -402,10 +402,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1093,10 +1089,10 @@
         <v>80</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>74</v>
@@ -1186,7 +1182,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="4" t="s">
         <v>88</v>
       </c>
       <c r="B32" s="1" t="n">

--- a/config/apartments.xlsx
+++ b/config/apartments.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="94">
   <si>
     <t xml:space="preserve">Квартира</t>
   </si>
@@ -293,6 +293,15 @@
   </si>
   <si>
     <t xml:space="preserve">Бабушкина</t>
+  </si>
+  <si>
+    <t xml:space="preserve">улица Михайлова, 12Б</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мама Жанны</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Финляндский</t>
   </si>
 </sst>
 </file>
@@ -303,7 +312,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -326,6 +335,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="1"/>
       <charset val="204"/>
     </font>
   </fonts>
@@ -371,7 +386,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -402,6 +417,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -527,7 +546,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultColWidth="11.5625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44.44"/>
@@ -1199,6 +1218,26 @@
       </c>
       <c r="G32" s="1" t="s">
         <v>90</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
